--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nolany/Developer/repos/WP-blog-agent/manual-files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NolanYoung\Developer\repos\WP-blog-agent\manual-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BB3330-8891-7645-96A2-24B0B9D1B70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45003664-11DE-4800-9655-42C4FFEEF03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blog tracker" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="67">
   <si>
     <t>blog_id</t>
   </si>
@@ -71,6 +71,156 @@
   </si>
   <si>
     <t>How to build a complete WordPress website from the ground up. This guide explains how WordPress works, how themes and plugins connect, and how key files and folders organize your site’s design, content, features, and functionality.</t>
+  </si>
+  <si>
+    <t>How to Build a Complete WordPress Website From the Ground Up. This guide explains how WordPress works, how themes and plugins connect, and how the core files and folders organize a site's design, content, features, and functionality.</t>
+  </si>
+  <si>
+    <t>How to Plan a WordPress Website Before Development Begins. Learn how to turn business goals into a clear sitemap, page plan, content checklist, feature scope, and launch roadmap before design or development starts.</t>
+  </si>
+  <si>
+    <t>Custom WordPress Theme vs. Prebuilt Theme: Which Is Right for Your Business? This guide compares cost, flexibility, performance, maintainability, and long-term ownership so teams can choose the right foundation for their website.</t>
+  </si>
+  <si>
+    <t>How the WordPress Template Hierarchy Controls Your Website. Learn how WordPress selects homepage, page, post, archive, category, search, and error templates—and why understanding that system makes custom theme work more reliable.</t>
+  </si>
+  <si>
+    <t>How to Build a Custom WordPress Theme That Is Easy to Maintain. This guide covers theme structure, reusable template parts, asset loading, settings, documentation, and development choices that make future updates less fragile.</t>
+  </si>
+  <si>
+    <t>What Is a WordPress Child Theme and When Should You Use One? Learn how child themes safely customize an existing theme, what they inherit, and when a custom theme or plugin-based solution is a better fit.</t>
+  </si>
+  <si>
+    <t>Gutenberg Blocks vs. Classic WordPress Templates: How to Choose Your Content System. This guide explains the tradeoffs between editable blocks, custom templates, reusable patterns, and hybrid approaches for a practical content workflow.</t>
+  </si>
+  <si>
+    <t>How Custom Post Types Make WordPress Easier to Manage. Learn how structured content types for services, projects, team members, testimonials, and resources keep a growing website organized and consistent.</t>
+  </si>
+  <si>
+    <t>How Custom Fields Improve WordPress Content Management. This guide explains how custom fields create repeatable page sections, support structured data, reduce editor mistakes, and make templates more flexible.</t>
+  </si>
+  <si>
+    <t>How to Choose WordPress Plugins Without Slowing Down Your Website. Learn how to evaluate plugin quality, compatibility, security, support, duplicate functionality, and long-term maintenance before adding another plugin.</t>
+  </si>
+  <si>
+    <t>How to Improve WordPress Website Speed Without Breaking the Design. This guide covers caching, asset loading, images, fonts, plugins, hosting, script cleanup, and careful testing so performance gains do not create new issues.</t>
+  </si>
+  <si>
+    <t>Understanding Core Web Vitals for WordPress Websites. Learn what loading speed, visual stability, and interactivity metrics mean, what commonly harms them, and how to prioritize fixes that improve the visitor experience.</t>
+  </si>
+  <si>
+    <t>How to Optimize Images for a Faster WordPress Website. This guide explains image formats, compression, responsive sizes, lazy loading, alt text, and media-library habits that improve page speed without sacrificing quality.</t>
+  </si>
+  <si>
+    <t>How to Launch a WooCommerce Store With a Strong Technical Foundation. Learn how products, payments, shipping, taxes, email, inventory, analytics, policies, and testing fit together before an online store goes live.</t>
+  </si>
+  <si>
+    <t>How to Build Better WooCommerce Product Pages. This guide explains the product information, images, variations, shipping details, trust signals, calls to action, and structured data that help shoppers make confident decisions.</t>
+  </si>
+  <si>
+    <t>How to Reduce Checkout Friction in WooCommerce. Learn how guest checkout, payment options, delivery information, form design, error messages, mobile usability, and testing can improve the path from cart to purchase.</t>
+  </si>
+  <si>
+    <t>How to Connect Inventory Systems to WooCommerce. This guide explains the planning, product matching, variation logic, stock updates, price synchronization, error handling, and reporting needed for a dependable inventory workflow.</t>
+  </si>
+  <si>
+    <t>How to Set Up WooCommerce Shipping Rules That Customers Understand. Learn how zones, delivery methods, pickup, product restrictions, rates, notices, and testing work together to create clear shipping expectations.</t>
+  </si>
+  <si>
+    <t>How to Safely Update WordPress Plugins and Themes. This guide covers backups, staging sites, compatibility checks, change logs, regression testing, rollback plans, and the disciplined process behind safe updates.</t>
+  </si>
+  <si>
+    <t>WordPress Security Basics Every Business Website Needs. Learn the practical safeguards that protect a site: updates, strong access controls, least-privilege roles, backups, secure forms, monitoring, and vulnerability response.</t>
+  </si>
+  <si>
+    <t>How to Create a WordPress Backup and Recovery Plan. This guide explains what to back up, how often to test restores, where to store copies, and how to recover safely from failed updates, outages, or accidental changes.</t>
+  </si>
+  <si>
+    <t>Why Every WordPress Website Needs a Staging Environment. Learn how a staging site separates experimentation from production, supports safer testing, and helps teams review updates before visitors see them.</t>
+  </si>
+  <si>
+    <t>How to Make a WordPress Website More Accessible. This guide covers semantic structure, headings, keyboard navigation, focus states, contrast, responsive behavior, forms, and content choices that support more visitors.</t>
+  </si>
+  <si>
+    <t>How to Build WordPress Forms That Capture the Right Information. Learn how to define form goals, choose useful fields, provide clear labels, validate entries, route notifications, and create a smoother inquiry process.</t>
+  </si>
+  <si>
+    <t>How to Protect WordPress Forms From Spam Without Hurting Conversions. This guide explains spam prevention, honeypots, rate limits, validation, CAPTCHA tradeoffs, logging, and testing for reliable form submissions.</t>
+  </si>
+  <si>
+    <t>How Cookie Consent and Privacy-Aware Tracking Work on a Website. Learn how consent choices affect analytics and marketing tools, which data should be minimized, and how to build a clearer visitor experience.</t>
+  </si>
+  <si>
+    <t>How to Set Up Google Analytics 4 for a Business Website. This guide explains the GA4 basics: property setup, data streams, key events, conversion definitions, internal traffic, reporting, and validation after launch.</t>
+  </si>
+  <si>
+    <t>How Google Tag Manager Makes Website Tracking Easier to Manage. Learn how GTM organizes tags, triggers, variables, consent settings, testing, and publishing so tracking changes are more controlled and auditable.</t>
+  </si>
+  <si>
+    <t>How to Track Website Leads and Sales Without Misleading Data. This guide explains conversion events, form submissions, calls, purchases, attribution, duplicate prevention, and QA practices that make reports trustworthy.</t>
+  </si>
+  <si>
+    <t>How to Audit Your Website Analytics Before Making Marketing Decisions. Learn how to find duplicate tags, missing events, broken conversions, referral issues, consent gaps, and reporting inconsistencies before acting on the numbers.</t>
+  </si>
+  <si>
+    <t>What Is Technical SEO and Why Does Your Website Need It? This guide explains crawlability, indexing, page structure, speed, internal links, metadata, canonical URLs, redirects, and other foundations search engines rely on.</t>
+  </si>
+  <si>
+    <t>How Schema Markup Helps Search Engines Understand Your Business. Learn what structured data is, which schema types fit common business pages, how it supports clearer search results, and how to validate implementation.</t>
+  </si>
+  <si>
+    <t>How to Improve Local SEO for a Service-Based Business. This guide covers location pages, service areas, business information consistency, reviews, local content, maps, and technical foundations that support local visibility.</t>
+  </si>
+  <si>
+    <t>How to Diagnose Indexing and Crawling Problems on a Website. Learn how search engines discover pages, why important content can be excluded, and how sitemaps, robots rules, redirects, canonicals, and page quality affect indexing.</t>
+  </si>
+  <si>
+    <t>How to Build a Website Content Architecture That Supports Growth. This guide explains how to organize services, resources, case studies, categories, internal links, navigation, and calls to action so visitors can find the next step.</t>
+  </si>
+  <si>
+    <t>How to Build a Business Blog Strategy That Produces Useful Content. Learn how to choose topics, match search intent, create content clusters, set realistic publishing goals, and connect posts to services without writing filler.</t>
+  </si>
+  <si>
+    <t>When Does a Business Website Need a Redesign? This guide helps teams recognize whether their real problem is visual design, unclear messaging, weak performance, outdated technology, poor conversion paths, or missing functionality.</t>
+  </si>
+  <si>
+    <t>How to Write Website Copy That Works With Your Design and User Journey. Learn how page hierarchy, headings, proof, service details, calls to action, and scannable content combine to help visitors understand what to do next.</t>
+  </si>
+  <si>
+    <t>How to Build a Website That Your Team Can Actually Maintain. This guide covers editable content systems, reusable sections, editor guidance, documentation, ownership, and technical decisions that reduce long-term dependence on a developer.</t>
+  </si>
+  <si>
+    <t>How Workflow Automation Can Remove Repetitive Business Tasks. Learn how to identify manual bottlenecks, define safe automation boundaries, connect systems, handle exceptions, and measure whether an automation is truly helping.</t>
+  </si>
+  <si>
+    <t>How to Plan a Reliable API Integration for Your Business. This guide explains data mapping, authentication, rate limits, synchronization timing, error handling, monitoring, and documentation before systems start exchanging data.</t>
+  </si>
+  <si>
+    <t>How Custom Admin Tools Can Simplify Internal Workflows. Learn how purpose-built dashboards and internal interfaces can reduce spreadsheet work, prevent repeated mistakes, and give teams clearer visibility into everyday operations.</t>
+  </si>
+  <si>
+    <t>When Does Your Business Need Custom Software Instead of Another SaaS Tool? This guide compares off-the-shelf software, integrations, workflow changes, and purpose-built tools so teams can invest where custom development adds real value.</t>
+  </si>
+  <si>
+    <t>How to Turn a Business Workflow Into a Useful Web Application. Learn how discovery, user roles, data models, interface decisions, security, testing, and rollout planning turn a real operational problem into a workable product.</t>
+  </si>
+  <si>
+    <t>How to Plan a Mobile App Before Writing Code. This guide helps businesses define the user problem, core features, platform needs, payments, notifications, analytics, security, and phased roadmap for a practical app launch.</t>
+  </si>
+  <si>
+    <t>How to Decide Between a Web App and a Mobile App. Learn the differences in access, device features, distribution, development cost, maintenance, and user behavior so your product starts on the right platform.</t>
+  </si>
+  <si>
+    <t>How to Build an Analytics Dashboard That Leads to Better Decisions. This guide explains how to choose meaningful metrics, connect clean sources, define reporting periods, clarify ownership, and avoid dashboards full of noise.</t>
+  </si>
+  <si>
+    <t>How to Use Website Reporting to Find Conversion Opportunities. Learn how to connect traffic, engagement, forms, calls, sales, search performance, and page behavior into a review process that identifies useful next actions.</t>
+  </si>
+  <si>
+    <t>How to Maintain a Website After Launch. This guide covers ongoing updates, backups, security, performance reviews, content changes, analytics QA, accessibility checks, and support practices that keep a digital presence dependable.</t>
+  </si>
+  <si>
+    <t>How to Choose the Right Digital Project for Your Next Business Investment. Learn how to prioritize a website refresh, performance pass, ecommerce improvement, tracking cleanup, automation, or custom tool based on business impact and readiness.</t>
   </si>
 </sst>
 </file>
@@ -184,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -208,11 +358,18 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -226,10 +383,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BlogTrackerTable" displayName="BlogTrackerTable" ref="A1:N2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BlogTrackerTable" displayName="BlogTrackerTable" ref="A1:N52" totalsRowShown="0">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="blog_id"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="blog_topic"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="blog_topic" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="blog_status"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="blog_created_date"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="blog_posted_date"/>
@@ -443,10 +600,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="2" max="2" width="48" style="9" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
@@ -459,7 +616,7 @@
     <col min="13" max="14" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32" customHeight="1">
+    <row r="1" spans="1:14" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="44" customHeight="1">
+    <row r="2" spans="1:14" ht="44.1" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -525,373 +682,673 @@
       <c r="M2" s="6"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" ht="71.25">
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" ht="71.25">
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" ht="71.25">
+      <c r="B5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" ht="71.25">
+      <c r="B6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" ht="71.25">
+      <c r="B7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" ht="57">
+      <c r="B8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" ht="71.25">
+      <c r="B9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" ht="71.25">
+      <c r="B10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" ht="71.25">
+      <c r="B11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" ht="71.25">
+      <c r="B12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" ht="71.25">
+      <c r="B13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" ht="71.25">
+      <c r="B14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" ht="71.25">
+      <c r="B15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" ht="57">
+      <c r="B16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" spans="4:14">
+    <row r="17" spans="2:14" ht="71.25">
+      <c r="B17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" spans="4:14">
+    <row r="18" spans="2:14" ht="71.25">
+      <c r="B18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="4:14">
+    <row r="19" spans="2:14" ht="71.25">
+      <c r="B19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="4:14">
+    <row r="20" spans="2:14" ht="71.25">
+      <c r="B20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" spans="4:14">
+    <row r="21" spans="2:14" ht="57">
+      <c r="B21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="4:14">
+    <row r="22" spans="2:14" ht="71.25">
+      <c r="B22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="4:14">
+    <row r="23" spans="2:14" ht="71.25">
+      <c r="B23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="4:14">
+    <row r="24" spans="2:14" ht="71.25">
+      <c r="B24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="4:14">
+    <row r="25" spans="2:14" ht="71.25">
+      <c r="B25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="4:14">
+    <row r="26" spans="2:14" ht="57">
+      <c r="B26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
     </row>
-    <row r="27" spans="4:14">
+    <row r="27" spans="2:14" ht="71.25">
+      <c r="B27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="4:14">
+    <row r="28" spans="2:14" ht="57">
+      <c r="B28" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
     </row>
-    <row r="29" spans="4:14">
+    <row r="29" spans="2:14" ht="57">
+      <c r="B29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="4:14">
+    <row r="30" spans="2:14" ht="71.25">
+      <c r="B30" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
     </row>
-    <row r="31" spans="4:14">
+    <row r="31" spans="2:14" ht="71.25">
+      <c r="B31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" spans="4:14">
+    <row r="32" spans="2:14" ht="71.25">
+      <c r="B32" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" spans="4:14">
+    <row r="33" spans="2:14" ht="71.25">
+      <c r="B33" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
     </row>
-    <row r="34" spans="4:14">
+    <row r="34" spans="2:14" ht="71.25">
+      <c r="B34" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" spans="4:14">
+    <row r="35" spans="2:14" ht="71.25">
+      <c r="B35" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" spans="4:14">
+    <row r="36" spans="2:14" ht="71.25">
+      <c r="B36" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" spans="4:14">
+    <row r="37" spans="2:14" ht="71.25">
+      <c r="B37" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" spans="4:14">
+    <row r="38" spans="2:14" ht="71.25">
+      <c r="B38" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" spans="4:14">
+    <row r="39" spans="2:14" ht="71.25">
+      <c r="B39" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="4:14">
+    <row r="40" spans="2:14" ht="71.25">
+      <c r="B40" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" spans="4:14">
+    <row r="41" spans="2:14" ht="71.25">
+      <c r="B41" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
     </row>
-    <row r="42" spans="4:14">
+    <row r="42" spans="2:14" ht="71.25">
+      <c r="B42" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
     </row>
-    <row r="43" spans="4:14">
+    <row r="43" spans="2:14" ht="71.25">
+      <c r="B43" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
     </row>
-    <row r="44" spans="4:14">
+    <row r="44" spans="2:14" ht="71.25">
+      <c r="B44" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
     </row>
-    <row r="45" spans="4:14">
+    <row r="45" spans="2:14" ht="71.25">
+      <c r="B45" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
     </row>
-    <row r="46" spans="4:14">
+    <row r="46" spans="2:14" ht="71.25">
+      <c r="B46" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
     </row>
-    <row r="47" spans="4:14">
+    <row r="47" spans="2:14" ht="71.25">
+      <c r="B47" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
     </row>
-    <row r="48" spans="4:14">
+    <row r="48" spans="2:14" ht="57">
+      <c r="B48" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
     </row>
-    <row r="49" spans="4:14">
+    <row r="49" spans="2:14" ht="71.25">
+      <c r="B49" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
     </row>
-    <row r="50" spans="4:14">
+    <row r="50" spans="2:14" ht="71.25">
+      <c r="B50" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
     </row>
-    <row r="51" spans="4:14">
+    <row r="51" spans="2:14" ht="71.25">
+      <c r="B51" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
     </row>
-    <row r="52" spans="4:14">
+    <row r="52" spans="2:14" ht="71.25">
+      <c r="B52" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
     </row>
-    <row r="53" spans="4:14">
+    <row r="53" spans="2:14">
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
     </row>
-    <row r="54" spans="4:14">
+    <row r="54" spans="2:14">
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
     </row>
-    <row r="55" spans="4:14">
+    <row r="55" spans="2:14">
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="4:14">
+    <row r="56" spans="2:14">
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
     </row>
-    <row r="57" spans="4:14">
+    <row r="57" spans="2:14">
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
     </row>
-    <row r="58" spans="4:14">
+    <row r="58" spans="2:14">
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="4:14">
+    <row r="59" spans="2:14">
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="4:14">
+    <row r="60" spans="2:14">
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="4:14">
+    <row r="61" spans="2:14">
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
     </row>
-    <row r="62" spans="4:14">
+    <row r="62" spans="2:14">
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
     </row>
-    <row r="63" spans="4:14">
+    <row r="63" spans="2:14">
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
     </row>
-    <row r="64" spans="4:14">
+    <row r="64" spans="2:14">
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="M64" s="7"/>

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -393,22 +393,31 @@
         <v>long</v>
       </c>
       <c r="E3" t="str">
-        <v>pending</v>
+        <v>posted</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-07-28T00:23:09.403Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-07-28T00:35:42.400Z</v>
+      </c>
+      <c r="H3" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0002-website-redesign-checklist-15-steps-before-you-hire.md</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>approved</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>YES 2 / NO 2</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>openai/gpt-oss-20b</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>28351</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28351</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -425,7 +434,22 @@
         <v>medium</v>
       </c>
       <c r="E4" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-07-28T00:26:46.795Z</v>
+      </c>
+      <c r="H4" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0003-web-design-vs-web-development.md</v>
+      </c>
+      <c r="I4" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J4" t="str">
+        <v>YES 3 / NO 3</v>
+      </c>
+      <c r="K4" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -3906,15 +3930,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="48.83203125" customWidth="1"/>
-    <col min="5" max="5" width="64.83203125" customWidth="1"/>
-    <col min="6" max="6" width="56.83203125" customWidth="1"/>
-    <col min="7" max="7" width="44.83203125" customWidth="1"/>
-    <col min="8" max="8" width="36.83203125" customWidth="1"/>
-    <col min="9" max="9" width="48.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="16.83203125"/>
+    <col min="2" max="2" customWidth="1" width="30.83203125"/>
+    <col min="3" max="3" customWidth="1" width="11.83203125"/>
+    <col min="4" max="4" customWidth="1" width="48.83203125"/>
+    <col min="5" max="5" customWidth="1" width="64.83203125"/>
+    <col min="6" max="6" customWidth="1" width="56.83203125"/>
+    <col min="7" max="7" customWidth="1" width="44.83203125"/>
+    <col min="8" max="8" customWidth="1" width="36.83203125"/>
+    <col min="9" max="9" customWidth="1" width="48.83203125"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -466,7 +466,22 @@
         <v>long</v>
       </c>
       <c r="E5" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-07-28T01:56:25.929Z</v>
+      </c>
+      <c r="H5" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0004-custom-website-cost-practical-budgeting-guide.md</v>
+      </c>
+      <c r="I5" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J5" t="str">
+        <v>YES 4 / NO 4</v>
+      </c>
+      <c r="K5" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -466,22 +466,31 @@
         <v>long</v>
       </c>
       <c r="E5" t="str">
-        <v>awaiting_review</v>
+        <v>posted</v>
       </c>
       <c r="F5" t="str">
         <v>2026-07-28T01:56:25.929Z</v>
       </c>
+      <c r="G5" t="str">
+        <v>2026-07-28T02:33:55.284Z</v>
+      </c>
       <c r="H5" t="str">
         <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0004-custom-website-cost-practical-budgeting-guide.md</v>
       </c>
       <c r="I5" t="str">
-        <v>pending</v>
+        <v>approved</v>
       </c>
       <c r="J5" t="str">
         <v>YES 4 / NO 4</v>
       </c>
       <c r="K5" t="str">
         <v>openai/gpt-oss-20b</v>
+      </c>
+      <c r="L5" t="str">
+        <v>28352</v>
+      </c>
+      <c r="M5" t="str">
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28352</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -498,7 +507,22 @@
         <v>medium</v>
       </c>
       <c r="E6" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-07-28T02:35:29.675Z</v>
+      </c>
+      <c r="H6" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0005-website-planning-checklist.md</v>
+      </c>
+      <c r="I6" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J6" t="str">
+        <v>YES 5 / NO 5</v>
+      </c>
+      <c r="K6" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -515,7 +539,22 @@
         <v>long</v>
       </c>
       <c r="E7" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-07-28T02:39:48.534Z</v>
+      </c>
+      <c r="H7" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0006-conversion-focused-website-design.md</v>
+      </c>
+      <c r="I7" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J7" t="str">
+        <v>YES 6 / NO 6</v>
+      </c>
+      <c r="K7" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -532,7 +571,22 @@
         <v>medium</v>
       </c>
       <c r="E8" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-07-28T02:42:43.615Z</v>
+      </c>
+      <c r="H8" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0007-b2b-website-design-best-practices.md</v>
+      </c>
+      <c r="I8" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J8" t="str">
+        <v>YES 7 / NO 7</v>
+      </c>
+      <c r="K8" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -549,7 +603,22 @@
         <v>short</v>
       </c>
       <c r="E9" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-07-28T02:44:47.751Z</v>
+      </c>
+      <c r="H9" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0008-website-navigation-best-practices-build-menus-that-help-user.md</v>
+      </c>
+      <c r="I9" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J9" t="str">
+        <v>YES 8 / NO 8</v>
+      </c>
+      <c r="K9" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -566,7 +635,22 @@
         <v>medium</v>
       </c>
       <c r="E10" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-07-28T02:47:44.815Z</v>
+      </c>
+      <c r="H10" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0009-website-accessibility-checklist-business-websites.md</v>
+      </c>
+      <c r="I10" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J10" t="str">
+        <v>YES 9 / NO 9</v>
+      </c>
+      <c r="K10" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -583,7 +667,22 @@
         <v>long</v>
       </c>
       <c r="E11" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-07-28T02:51:01.511Z</v>
+      </c>
+      <c r="H11" t="str">
+        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0010-custom-wordpress-development-vs-page-builders.md</v>
+      </c>
+      <c r="I11" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J11" t="str">
+        <v>YES 10 / NO 10</v>
+      </c>
+      <c r="K11" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -600,6 +699,9 @@
         <v>long</v>
       </c>
       <c r="E12" t="str">
+        <v>generating</v>
+      </c>
+      <c r="I12" t="str">
         <v>pending</v>
       </c>
     </row>

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -38,11 +38,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="0"/>
-    <numFmt numFmtId="201" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="202" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -75,9 +73,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -275,6 +273,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -719,7 +719,22 @@
         <v>medium</v>
       </c>
       <c r="E13" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-07-28T15:37:56.579Z</v>
+      </c>
+      <c r="H13" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0012-choose-wordpress-development-agency.md</v>
+      </c>
+      <c r="I13" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J13" t="str">
+        <v>YES 12 / NO 12</v>
+      </c>
+      <c r="K13" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -736,7 +751,22 @@
         <v>medium</v>
       </c>
       <c r="E14" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-07-28T15:40:46.445Z</v>
+      </c>
+      <c r="H14" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0013-wordpress-security-best-practices-business-websites.md</v>
+      </c>
+      <c r="I14" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J14" t="str">
+        <v>YES 13 / NO 13</v>
+      </c>
+      <c r="K14" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -753,7 +783,22 @@
         <v>long</v>
       </c>
       <c r="E15" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-07-28T15:43:28.448Z</v>
+      </c>
+      <c r="H15" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0014-wordpress-website-faster-core-web-vitals-guide.md</v>
+      </c>
+      <c r="I15" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J15" t="str">
+        <v>YES 14 / NO 14</v>
+      </c>
+      <c r="K15" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -770,7 +815,31 @@
         <v>medium</v>
       </c>
       <c r="E16" t="str">
-        <v>pending</v>
+        <v>posted</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-07-28T16:36:30.544Z</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-07-28T16:38:20.227Z</v>
+      </c>
+      <c r="H16" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0015-website-performance-optimization-checklist-improve-speed-wit.md</v>
+      </c>
+      <c r="I16" t="str">
+        <v>approved</v>
+      </c>
+      <c r="J16" t="str">
+        <v>YES 15 / NO 15</v>
+      </c>
+      <c r="K16" t="str">
+        <v>openai/gpt-oss-20b</v>
+      </c>
+      <c r="L16" t="str">
+        <v>28353</v>
+      </c>
+      <c r="M16" t="str">
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28353</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -787,7 +856,22 @@
         <v>long</v>
       </c>
       <c r="E17" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-07-28T16:40:10.574Z</v>
+      </c>
+      <c r="H17" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0016-plan-high-converting-landing-page.md</v>
+      </c>
+      <c r="I17" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J17" t="str">
+        <v>YES 16 / NO 16</v>
+      </c>
+      <c r="K17" t="str">
+        <v>openai/gpt-oss-20b, qwen/qwen2.5-coder-14b</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -804,7 +888,22 @@
         <v>short</v>
       </c>
       <c r="E18" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-07-28T16:41:45.249Z</v>
+      </c>
+      <c r="H18" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0017-landing-page-vs-website-business-needs-each.md</v>
+      </c>
+      <c r="I18" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J18" t="str">
+        <v>YES 17 / NO 17</v>
+      </c>
+      <c r="K18" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -823,6 +922,9 @@
       <c r="E19" t="str">
         <v>pending</v>
       </c>
+      <c r="I19" t="str">
+        <v>pending</v>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" t="str">
@@ -838,7 +940,22 @@
         <v>long</v>
       </c>
       <c r="E20" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-07-28T15:54:29.639Z</v>
+      </c>
+      <c r="H20" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0019-ecommerce-website-checklist-before-launch.md</v>
+      </c>
+      <c r="I20" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J20" t="str">
+        <v>YES 19 / NO 19</v>
+      </c>
+      <c r="K20" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -855,6 +972,9 @@
         <v>medium</v>
       </c>
       <c r="E21" t="str">
+        <v>error</v>
+      </c>
+      <c r="I21" t="str">
         <v>pending</v>
       </c>
     </row>
@@ -2373,7 +2493,7 @@
       </c>
       <c r="B2" s="1">
         <f>COUNTIF('Blog tracker'!$E$3:$E$52,"pending")</f>
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C2" t="str">
         <v>Planned words</v>
@@ -4101,27 +4221,27 @@
         <v>A comprehensive article with ten H1 sections for topics that need context, planning, detailed guidance, and evaluation.</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. introduction: Introduce the reader's problem and the guide's outcome.
-2. problem-context: Describe the underlying problem or opportunity.
-3. foundations: Establish definitions and foundational knowledge.
-4. planning: Show how to prepare, scope, or organize the work.
-5. approach-one: Develop the first major part of the solution or evaluation.
-6. approach-two: Develop the second major part of the solution or evaluation.
-7. approach-three: Develop the third major part of the solution or evaluation.
-8. common-mistakes: Identify avoidable mistakes, risks, or weak approaches.
-9. measurement-checklist: Show how to evaluate quality, completion, or results.
+        <v xml:space="preserve">1. introduction: Introduce the reader's problem and the guide's outcome._x000d__x000d_
+2. problem-context: Describe the underlying problem or opportunity._x000d__x000d_
+3. foundations: Establish definitions and foundational knowledge._x000d__x000d_
+4. planning: Show how to prepare, scope, or organize the work._x000d__x000d_
+5. approach-one: Develop the first major part of the solution or evaluation._x000d__x000d_
+6. approach-two: Develop the second major part of the solution or evaluation._x000d__x000d_
+7. approach-three: Develop the third major part of the solution or evaluation._x000d__x000d_
+8. common-mistakes: Identify avoidable mistakes, risks, or weak approaches._x000d__x000d_
+9. measurement-checklist: Show how to evaluate quality, completion, or results._x000d__x000d_
 10. conclusion: Summarize the guide and recommend the most useful next step.</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">introduction: 1-3 paragraphs, 35-220 words each
-problem-context: 1-4 paragraphs, 35-220 words each
-foundations: 1-4 paragraphs, 35-220 words each
-planning: 1-4 paragraphs, 35-220 words each
-approach-one: 1-4 paragraphs, 35-220 words each
-approach-two: 1-4 paragraphs, 35-220 words each
-approach-three: 1-4 paragraphs, 35-220 words each
-common-mistakes: 1-4 paragraphs, 35-220 words each
-measurement-checklist: 1-4 paragraphs, 35-220 words each
+        <v xml:space="preserve">introduction: 1-3 paragraphs, 35-220 words each_x000d__x000d_
+problem-context: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+foundations: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+planning: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+approach-one: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+approach-two: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+approach-three: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+common-mistakes: 1-4 paragraphs, 35-220 words each_x000d__x000d_
+measurement-checklist: 1-4 paragraphs, 35-220 words each_x000d__x000d_
 conclusion: 1-3 paragraphs, 35-220 words each</v>
       </c>
       <c r="G2" t="str">
@@ -4148,19 +4268,19 @@
         <v>A balanced article with six H1 sections, enough depth for explanation and implementation guidance.</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. introduction: Introduce the reader's situation and the article's practical outcome.
-2. foundations: Define the topic and establish the essential background.
-3. key-considerations: Explain the major factors the reader should evaluate.
-4. recommended-approach: Present a practical method, framework, or sequence.
-5. mistakes-and-measurement: Help the reader avoid predictable mistakes and recognize success.
+        <v xml:space="preserve">1. introduction: Introduce the reader's situation and the article's practical outcome._x000d__x000d_
+2. foundations: Define the topic and establish the essential background._x000d__x000d_
+3. key-considerations: Explain the major factors the reader should evaluate._x000d__x000d_
+4. recommended-approach: Present a practical method, framework, or sequence._x000d__x000d_
+5. mistakes-and-measurement: Help the reader avoid predictable mistakes and recognize success._x000d__x000d_
 6. conclusion: Bring the guidance together and recommend a relevant next step.</v>
       </c>
       <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">introduction: 1-3 paragraphs, 40-240 words each
-foundations: 1-4 paragraphs, 40-240 words each
-key-considerations: 1-4 paragraphs, 40-240 words each
-recommended-approach: 1-4 paragraphs, 40-240 words each
-mistakes-and-measurement: 1-4 paragraphs, 40-240 words each
+        <v xml:space="preserve">introduction: 1-3 paragraphs, 40-240 words each_x000d__x000d_
+foundations: 1-4 paragraphs, 40-240 words each_x000d__x000d_
+key-considerations: 1-4 paragraphs, 40-240 words each_x000d__x000d_
+recommended-approach: 1-4 paragraphs, 40-240 words each_x000d__x000d_
+mistakes-and-measurement: 1-4 paragraphs, 40-240 words each_x000d__x000d_
 conclusion: 1-3 paragraphs, 40-240 words each</v>
       </c>
       <c r="G3" t="str">
@@ -4187,15 +4307,15 @@
         <v>A focused article with four substantial H1 sections and a direct conclusion.</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. introduction: Introduce the topic, reader problem, and practical promise of the article.
-2. core-explanation: Explain the central idea and why it matters.
-3. practical-guidance: Turn the explanation into practical actions or recommendations.
+        <v xml:space="preserve">1. introduction: Introduce the topic, reader problem, and practical promise of the article._x000d__x000d_
+2. core-explanation: Explain the central idea and why it matters._x000d__x000d_
+3. practical-guidance: Turn the explanation into practical actions or recommendations._x000d__x000d_
 4. conclusion: Summarize the takeaway and give the reader a sensible next step.</v>
       </c>
       <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">introduction: 1-3 paragraphs, 45-250 words each
-core-explanation: 1-4 paragraphs, 45-250 words each
-practical-guidance: 1-4 paragraphs, 45-250 words each
+        <v xml:space="preserve">introduction: 1-3 paragraphs, 45-250 words each_x000d__x000d_
+core-explanation: 1-4 paragraphs, 45-250 words each_x000d__x000d_
+practical-guidance: 1-4 paragraphs, 45-250 words each_x000d__x000d_
 conclusion: 1-2 paragraphs, 45-250 words each</v>
       </c>
       <c r="G4" t="str">
@@ -4210,6 +4330,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -920,7 +920,7 @@
         <v>long</v>
       </c>
       <c r="E19" t="str">
-        <v>pending</v>
+        <v>generating</v>
       </c>
       <c r="I19" t="str">
         <v>pending</v>

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -920,7 +920,7 @@
         <v>long</v>
       </c>
       <c r="E19" t="str">
-        <v>generating</v>
+        <v>error</v>
       </c>
       <c r="I19" t="str">
         <v>pending</v>
@@ -992,7 +992,22 @@
         <v>long</v>
       </c>
       <c r="E22" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-07-28T16:47:37.646Z</v>
+      </c>
+      <c r="H22" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0021-website-migration-checklist-relaunch-without-losing-seo.md</v>
+      </c>
+      <c r="I22" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J22" t="str">
+        <v>YES 21 / NO 21</v>
+      </c>
+      <c r="K22" t="str">
+        <v>openai/gpt-oss-20b, qwen/qwen2.5-coder-14b</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -1853,22 +1853,31 @@
         <v>medium</v>
       </c>
       <c r="D53" t="str">
-        <v>awaiting_review</v>
+        <v>posted</v>
       </c>
       <c r="E53" t="str">
         <v>2026-07-29T16:03:59.550Z</v>
       </c>
+      <c r="F53" t="str">
+        <v>2026-07-29T16:07:00.244Z</v>
+      </c>
       <c r="G53" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0052-choose-web-design-company-12-questions.md</v>
       </c>
       <c r="H53" t="str">
-        <v>pending</v>
+        <v>approved</v>
       </c>
       <c r="I53" t="str">
         <v>YES 52 / NO 52</v>
       </c>
       <c r="J53" t="str">
         <v>openai/gpt-oss-20b</v>
+      </c>
+      <c r="K53" t="str">
+        <v>28356</v>
+      </c>
+      <c r="L53" t="str">
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28356</v>
       </c>
     </row>
     <row r="54">
@@ -1882,7 +1891,22 @@
         <v>long</v>
       </c>
       <c r="D54" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2026-07-29T16:08:17.513Z</v>
+      </c>
+      <c r="G54" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0053-responsive-web-design-best-practices-mobile-first-business-w.md</v>
+      </c>
+      <c r="H54" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I54" t="str">
+        <v>YES 53 / NO 53</v>
+      </c>
+      <c r="J54" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="55">
@@ -1896,7 +1920,22 @@
         <v>long</v>
       </c>
       <c r="D55" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2026-07-29T16:15:01.606Z</v>
+      </c>
+      <c r="G55" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0054-wordpress-vs-webflow-best-cms-growing-business.md</v>
+      </c>
+      <c r="H55" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I55" t="str">
+        <v>YES 54 / NO 54</v>
+      </c>
+      <c r="J55" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="56">
@@ -3610,7 +3649,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C1000">
-      <formula1>"short,medium,long"</formula1>
+      <formula1>"how-to,long,medium,practical-guidance,short"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -1949,7 +1949,31 @@
         <v>long</v>
       </c>
       <c r="D56" t="str">
-        <v>pending</v>
+        <v>posted</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-07-29T18:34:54.584Z</v>
+      </c>
+      <c r="F56" t="str">
+        <v>2026-07-29T18:52:44.195Z</v>
+      </c>
+      <c r="G56" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0055-wordpress-vs-squarespace-which-platform-fits-your-business.md</v>
+      </c>
+      <c r="H56" t="str">
+        <v>approved</v>
+      </c>
+      <c r="I56" t="str">
+        <v>YES 55 / NO 55</v>
+      </c>
+      <c r="J56" t="str">
+        <v>openai/gpt-oss-20b</v>
+      </c>
+      <c r="K56" t="str">
+        <v>28357</v>
+      </c>
+      <c r="L56" t="str">
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28357</v>
       </c>
     </row>
     <row r="57">
@@ -1963,7 +1987,22 @@
         <v>long</v>
       </c>
       <c r="D57" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2026-07-29T18:54:00.132Z</v>
+      </c>
+      <c r="G57" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0056-headless-wordpress-explained-benefits-costs-when-it-makes-se.md</v>
+      </c>
+      <c r="H57" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I57" t="str">
+        <v>YES 56 / NO 56</v>
+      </c>
+      <c r="J57" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="58">
@@ -1977,7 +2016,22 @@
         <v>medium</v>
       </c>
       <c r="D58" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-07-29T19:05:36.781Z</v>
+      </c>
+      <c r="G58" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0057-website-redesign-roi-business-case.md</v>
+      </c>
+      <c r="H58" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I58" t="str">
+        <v>YES 57 / NO 57</v>
+      </c>
+      <c r="J58" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="59">
@@ -1991,7 +2045,22 @@
         <v>medium</v>
       </c>
       <c r="D59" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2026-07-29T19:07:32.852Z</v>
+      </c>
+      <c r="G59" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0058-website-discovery-phase-guide.md</v>
+      </c>
+      <c r="H59" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I59" t="str">
+        <v>YES 58 / NO 58</v>
+      </c>
+      <c r="J59" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="60">
@@ -2005,7 +2074,22 @@
         <v>long</v>
       </c>
       <c r="D60" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-07-29T20:24:37.237Z</v>
+      </c>
+      <c r="G60" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0059-ux-audit-checklist-find-friction-cost-leads.md</v>
+      </c>
+      <c r="H60" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I60" t="str">
+        <v>YES 59 / NO 59</v>
+      </c>
+      <c r="J60" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="61">

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -2103,7 +2103,22 @@
         <v>short</v>
       </c>
       <c r="D61" t="str">
-        <v>pending</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2026-07-29T21:09:00.049Z</v>
+      </c>
+      <c r="G61" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0060-mobile-first-web-design-why-businesses-need-it.md</v>
+      </c>
+      <c r="H61" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I61" t="str">
+        <v>YES 60 / NO 60</v>
+      </c>
+      <c r="J61" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="62">

--- a/manual-files/wordpress-blog-content-tracker.xlsx
+++ b/manual-files/wordpress-blog-content-tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -67,7 +67,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -265,6 +265,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -331,20 +333,23 @@
       <c r="B2" t="str">
         <v>How to build a complete WordPress website from the ground up. This guide explains how WordPress works, how themes and plugins connect, and how key files and folders organize your site’s design, content, features, and functionality.</v>
       </c>
+      <c r="C2" t="str">
+        <v>short</v>
+      </c>
       <c r="D2" t="str">
-        <v>posted</v>
-      </c>
-      <c r="E2" s="1">
-        <v>46230.66897849537</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-07-30T23:33:20.467Z</v>
       </c>
       <c r="F2" s="1">
         <v>46230.6901827662</v>
       </c>
       <c r="G2" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/1-how-to-build-a-complete-wordpress-website-from-the-ground-up-this-guide-explains.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0001-build-wordpress-site-from-scratch.md</v>
       </c>
       <c r="H2" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I2" t="str">
         <v>YES 1 / NO 1</v>
@@ -367,22 +372,22 @@
         <v>Website Redesign Checklist: 15 Steps Before You Hire a Web Design Agency</v>
       </c>
       <c r="C3" t="str">
-        <v>long</v>
+        <v>medium</v>
       </c>
       <c r="D3" t="str">
-        <v>posted</v>
-      </c>
-      <c r="E3" s="1">
-        <v>46231.01608105324</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46231.0247962963</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-07-30T23:36:05.031Z</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-07-30T19:24:40.444Z</v>
       </c>
       <c r="G3" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0002-website-redesign-checklist-15-steps-before-you-hire.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0002-website-redesign-checklist-15-steps-before-hire-agency.md</v>
       </c>
       <c r="H3" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I3" t="str">
         <v>YES 2 / NO 2</v>
@@ -391,10 +396,10 @@
         <v>openai/gpt-oss-20b</v>
       </c>
       <c r="K3" t="str">
-        <v>28351</v>
+        <v>28359</v>
       </c>
       <c r="L3" t="str">
-        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28351</v>
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28359</v>
       </c>
     </row>
     <row r="4">
@@ -405,16 +410,16 @@
         <v>Web Design vs. Web Development: What Growing Businesses Need to Know</v>
       </c>
       <c r="C4" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D4" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E4" s="1">
-        <v>46231.01859716435</v>
+      <c r="E4" t="str">
+        <v>2026-07-30T23:38:45.629Z</v>
       </c>
       <c r="G4" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0003-web-design-vs-web-development.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0003-web-design-vs-web-development-what-growing-businesses-need-t.md</v>
       </c>
       <c r="H4" t="str">
         <v>pending</v>
@@ -434,22 +439,22 @@
         <v>How Much Does a Custom Website Cost? A Practical Budgeting Guide</v>
       </c>
       <c r="C5" t="str">
-        <v>long</v>
+        <v>how-to</v>
       </c>
       <c r="D5" t="str">
-        <v>posted</v>
-      </c>
-      <c r="E5" s="1">
-        <v>46231.080855659726</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-07-30T23:42:29.376Z</v>
       </c>
       <c r="F5" s="1">
         <v>46231.10688986111</v>
       </c>
       <c r="G5" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0004-custom-website-cost-practical-budgeting-guide.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0004-custom-website-cost-practical-budgeting-guide.md</v>
       </c>
       <c r="H5" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I5" t="str">
         <v>YES 4 / NO 4</v>
@@ -472,16 +477,16 @@
         <v>Website Planning Checklist: What to Prepare Before a New Website Project</v>
       </c>
       <c r="C6" t="str">
-        <v>medium</v>
+        <v>practical-guidance</v>
       </c>
       <c r="D6" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E6" s="1">
-        <v>46231.10798234954</v>
+      <c r="E6" t="str">
+        <v>2026-07-30T23:45:07.015Z</v>
       </c>
       <c r="G6" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0005-website-planning-checklist.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0005-website-planning-checklist-what-to-prepare-before-a-new-webs.md</v>
       </c>
       <c r="H6" t="str">
         <v>pending</v>
@@ -506,11 +511,11 @@
       <c r="D7" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E7" s="1">
-        <v>46231.11097840278</v>
+      <c r="E7" t="str">
+        <v>2026-07-30T23:50:16.938Z</v>
       </c>
       <c r="G7" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0006-conversion-focused-website-design.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0006-conversion-focused-website-design-turn-visitors-into-leads.md</v>
       </c>
       <c r="H7" t="str">
         <v>pending</v>
@@ -530,16 +535,16 @@
         <v>B2B Website Design Best Practices for Clearer Buying Journeys</v>
       </c>
       <c r="C8" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D8" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E8" s="1">
-        <v>46231.11300480324</v>
+      <c r="E8" t="str">
+        <v>2026-07-30T23:52:28.099Z</v>
       </c>
       <c r="G8" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0007-b2b-website-design-best-practices.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0007-b2b-website-design-best-practices-clearer-buying-journeys.md</v>
       </c>
       <c r="H8" t="str">
         <v>pending</v>
@@ -559,16 +564,16 @@
         <v>Website Navigation Best Practices: Build Menus That Help Users Convert</v>
       </c>
       <c r="C9" t="str">
-        <v>short</v>
+        <v>long</v>
       </c>
       <c r="D9" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E9" s="1">
-        <v>46231.1144415625</v>
+      <c r="E9" t="str">
+        <v>2026-07-30T23:54:58.819Z</v>
       </c>
       <c r="G9" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0008-website-navigation-best-practices-build-menus-that-help-user.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0008-website-navigation-best-practices-build-menus-that-help-user.md</v>
       </c>
       <c r="H9" t="str">
         <v>pending</v>
@@ -588,16 +593,16 @@
         <v>Website Accessibility Checklist for Business Websites</v>
       </c>
       <c r="C10" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D10" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E10" s="1">
-        <v>46231.116490914355</v>
+      <c r="E10" t="str">
+        <v>2026-07-30T23:58:30.060Z</v>
       </c>
       <c r="G10" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0009-website-accessibility-checklist-business-websites.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0009-website-accessibility-checklist-business-websites.md</v>
       </c>
       <c r="H10" t="str">
         <v>pending</v>
@@ -622,11 +627,11 @@
       <c r="D11" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E11" s="1">
-        <v>46231.11876748843</v>
+      <c r="E11" t="str">
+        <v>2026-07-31T00:01:19.214Z</v>
       </c>
       <c r="G11" t="str">
-        <v>/Users/grasshopper/Developer/repos/WP-blog-agent/data/drafts/blog-0010-custom-wordpress-development-vs-page-builders.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0010-custom-wordpress-development-vs-page-builders.md</v>
       </c>
       <c r="H11" t="str">
         <v>pending</v>
@@ -649,10 +654,22 @@
         <v>long</v>
       </c>
       <c r="D12" t="str">
-        <v>generating</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-07-31T00:04:23.873Z</v>
+      </c>
+      <c r="G12" t="str">
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0011-wordpress-maintenance-checklist-updates-backups-security-per.md</v>
       </c>
       <c r="H12" t="str">
         <v>pending</v>
+      </c>
+      <c r="I12" t="str">
+        <v>YES 11 / NO 11</v>
+      </c>
+      <c r="J12" t="str">
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="13">
@@ -663,16 +680,16 @@
         <v>How to Choose a WordPress Development Agency for a Business Website</v>
       </c>
       <c r="C13" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D13" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E13" s="1">
-        <v>46231.651349293985</v>
+      <c r="E13" t="str">
+        <v>2026-07-31T00:07:19.039Z</v>
       </c>
       <c r="G13" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0012-choose-wordpress-development-agency.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0012-choose-wordpress-development-agency-for-business-website.md</v>
       </c>
       <c r="H13" t="str">
         <v>pending</v>
@@ -692,13 +709,13 @@
         <v>WordPress Security Best Practices for Business Websites</v>
       </c>
       <c r="C14" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D14" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E14" s="1">
-        <v>46231.65331533565</v>
+      <c r="E14" t="str">
+        <v>2026-07-31T00:09:59.958Z</v>
       </c>
       <c r="G14" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0013-wordpress-security-best-practices-business-websites.md</v>
@@ -726,11 +743,11 @@
       <c r="D15" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E15" s="1">
-        <v>46231.65519037037</v>
+      <c r="E15" t="str">
+        <v>2026-07-31T00:13:23.581Z</v>
       </c>
       <c r="G15" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0014-wordpress-website-faster-core-web-vitals-guide.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0014-make-wordpress-website-faster-core-web-vitals-guide.md</v>
       </c>
       <c r="H15" t="str">
         <v>pending</v>
@@ -750,22 +767,22 @@
         <v>Website Performance Optimization Checklist: Improve Speed Without Breaking Your Site</v>
       </c>
       <c r="C16" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D16" t="str">
-        <v>posted</v>
-      </c>
-      <c r="E16" s="1">
-        <v>46231.69202018518</v>
+        <v>awaiting_review</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-07-31T00:17:07.345Z</v>
       </c>
       <c r="F16" s="1">
         <v>46231.69328966435</v>
       </c>
       <c r="G16" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0015-website-performance-optimization-checklist-improve-speed-wit.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0015-website-performance-optimization-checklist.md</v>
       </c>
       <c r="H16" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I16" t="str">
         <v>YES 15 / NO 15</v>
@@ -793,11 +810,11 @@
       <c r="D17" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E17" s="1">
-        <v>46231.6945668287</v>
+      <c r="E17" t="str">
+        <v>2026-07-31T00:22:18.426Z</v>
       </c>
       <c r="G17" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0016-plan-high-converting-landing-page.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0016-how-to-plan-a-high-converting-landing-page.md</v>
       </c>
       <c r="H17" t="str">
         <v>pending</v>
@@ -806,7 +823,7 @@
         <v>YES 16 / NO 16</v>
       </c>
       <c r="J17" t="str">
-        <v>openai/gpt-oss-20b, qwen/qwen2.5-coder-14b</v>
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="18">
@@ -817,16 +834,16 @@
         <v>Landing Page vs. Website: When Your Business Needs Each</v>
       </c>
       <c r="C18" t="str">
-        <v>short</v>
+        <v>long</v>
       </c>
       <c r="D18" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E18" s="1">
-        <v>46231.695662604165</v>
+      <c r="E18" t="str">
+        <v>2026-07-31T00:25:32.288Z</v>
       </c>
       <c r="G18" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0017-landing-page-vs-website-business-needs-each.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0017-landing-page-vs-website-when-your-business-needs-each.md</v>
       </c>
       <c r="H18" t="str">
         <v>pending</v>
@@ -852,10 +869,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-29T12:09:16.549Z</v>
+        <v>2026-07-31T00:29:39.739Z</v>
       </c>
       <c r="G19" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0018-woocommerce-vs-shopify-choosing-right-ecommerce-platform.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0018-woocommerce-vs-shopify-choosing-the-right-ecommerce-platform.md</v>
       </c>
       <c r="H19" t="str">
         <v>pending</v>
@@ -880,11 +897,11 @@
       <c r="D20" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E20" s="1">
-        <v>46231.66284304398</v>
+      <c r="E20" t="str">
+        <v>2026-07-31T00:34:18.845Z</v>
       </c>
       <c r="G20" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0019-ecommerce-website-checklist-before-launch.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0019-ecommerce-website-checklist-plan-before-launch.md</v>
       </c>
       <c r="H20" t="str">
         <v>pending</v>
@@ -904,16 +921,16 @@
         <v>Ecommerce Product Page Best Practices That Support More Sales</v>
       </c>
       <c r="C21" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D21" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-29T13:36:05.740Z</v>
+        <v>2026-07-31T00:37:52.433Z</v>
       </c>
       <c r="G21" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0020-ecommerce-product-page-best-practices.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0020-ecommerce-product-page-best-practices-that-support-more-sale.md</v>
       </c>
       <c r="H21" t="str">
         <v>pending</v>
@@ -938,11 +955,11 @@
       <c r="D22" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E22" s="1">
-        <v>46231.69974127315</v>
+      <c r="E22" t="str">
+        <v>2026-07-31T00:41:19.859Z</v>
       </c>
       <c r="G22" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0021-website-migration-checklist-relaunch-without-losing-seo.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0021-website-migration-checklist-how-to-relaunch-without-losing-s.md</v>
       </c>
       <c r="H22" t="str">
         <v>pending</v>
@@ -951,7 +968,7 @@
         <v>YES 21 / NO 21</v>
       </c>
       <c r="J22" t="str">
-        <v>openai/gpt-oss-20b, qwen/qwen2.5-coder-14b</v>
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="23">
@@ -962,13 +979,13 @@
         <v>How to Measure Website Conversion Rate and Find Drop-Off Points</v>
       </c>
       <c r="C23" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D23" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-29T13:37:55.192Z</v>
+        <v>2026-07-31T00:44:07.753Z</v>
       </c>
       <c r="G23" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0022-measure-website-conversion-rate-drop-off-points.md</v>
@@ -991,16 +1008,16 @@
         <v>Website Analytics for Small Businesses: Metrics That Actually Matter</v>
       </c>
       <c r="C24" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D24" t="str">
         <v>awaiting_review</v>
       </c>
-      <c r="E24" s="1">
-        <v>46231.73590177084</v>
+      <c r="E24" t="str">
+        <v>2026-07-31T00:47:49.392Z</v>
       </c>
       <c r="G24" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0023-website-analytics-small-business-metrics-that-matter.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0023-website-analytics-small-business-metrics-that-actually-matte.md</v>
       </c>
       <c r="H24" t="str">
         <v>pending</v>
@@ -1009,7 +1026,7 @@
         <v>YES 23 / NO 23</v>
       </c>
       <c r="J24" t="str">
-        <v>openai/gpt-oss-20b, qwen/qwen2.5-coder-14b</v>
+        <v>openai/gpt-oss-20b</v>
       </c>
     </row>
     <row r="25">
@@ -1026,10 +1043,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-29T13:40:12.859Z</v>
+        <v>2026-07-31T00:51:36.476Z</v>
       </c>
       <c r="G25" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0024-website-content-strategy-sales.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0024-website-content-strategy-supports-sales.md</v>
       </c>
       <c r="H25" t="str">
         <v>pending</v>
@@ -1049,13 +1066,13 @@
         <v>Web Design Brief Template: What to Include Before Your Project Starts</v>
       </c>
       <c r="C26" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D26" t="str">
-        <v>awaiting_review</v>
+        <v>error</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-29T13:42:01.156Z</v>
+        <v>2026-07-31T00:54:55.112Z</v>
       </c>
       <c r="G26" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0025-web-design-brief-template-before-project-starts.md</v>
@@ -1084,10 +1101,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-29T13:44:17.970Z</v>
+        <v>2026-07-31T00:58:40.894Z</v>
       </c>
       <c r="G27" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0026-workflow-automation-ideas-10-manual-processes.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0026-workflow-automation-ideas-10-manual-processes-businesses-can.md</v>
       </c>
       <c r="H27" t="str">
         <v>pending</v>
@@ -1107,16 +1124,16 @@
         <v>What Is Workflow Automation? A Practical Guide for Growing Teams</v>
       </c>
       <c r="C28" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D28" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-29T13:46:07.481Z</v>
+        <v>2026-07-31T01:01:50.778Z</v>
       </c>
       <c r="G28" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0027-workflow-automation-practical-guide-growing-teams.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0027-what-is-workflow-automation-practical-guide-for-growing-team.md</v>
       </c>
       <c r="H28" t="str">
         <v>pending</v>
@@ -1139,7 +1156,7 @@
         <v>long</v>
       </c>
       <c r="D29" t="str">
-        <v>awaiting_review</v>
+        <v>error</v>
       </c>
       <c r="E29" t="str">
         <v>2026-07-29T13:48:20.187Z</v>
@@ -1171,7 +1188,7 @@
         <v>awaiting_review</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-29T13:50:34.743Z</v>
+        <v>2026-07-31T01:15:33.220Z</v>
       </c>
       <c r="G30" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0029-custom-crm-development-when-tailored-system-makes-sense.md</v>
@@ -1194,13 +1211,13 @@
         <v>API Integration for Businesses: What It Is and When You Need It</v>
       </c>
       <c r="C31" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D31" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-29T13:52:21.221Z</v>
+        <v>2026-07-31T01:36:09.416Z</v>
       </c>
       <c r="G31" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0030-api-integration-for-businesses-what-it-is-and-when-you-need-.md</v>
@@ -1223,13 +1240,13 @@
         <v>Internal Tools for Businesses: How Custom Admin Dashboards Save Time</v>
       </c>
       <c r="C32" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D32" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-29T13:54:07.623Z</v>
+        <v>2026-07-31T01:39:24.591Z</v>
       </c>
       <c r="G32" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0031-internal-tools-custom-admin-dashboards-save-time.md</v>
@@ -1258,10 +1275,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-29T13:56:17.786Z</v>
+        <v>2026-07-31T01:42:16.916Z</v>
       </c>
       <c r="G33" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0032-bpa-best-first-project.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0032-business-process-automation-best-first-project.md</v>
       </c>
       <c r="H33" t="str">
         <v>pending</v>
@@ -1287,7 +1304,7 @@
         <v>awaiting_review</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-29T13:58:35.142Z</v>
+        <v>2026-07-31T01:45:41.559Z</v>
       </c>
       <c r="G34" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0033-custom-software-development-process-discovery-launch.md</v>
@@ -1313,22 +1330,31 @@
         <v>long</v>
       </c>
       <c r="D35" t="str">
-        <v>awaiting_review</v>
+        <v>posted</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-29T14:00:48.473Z</v>
+        <v>2026-07-31T01:49:20.358Z</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2026-07-31T02:01:43.768Z</v>
       </c>
       <c r="G35" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0034-mobile-app-development-process-idea-to-launch.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0034-mobile-app-development-process-from-idea-to-app-store-launch.md</v>
       </c>
       <c r="H35" t="str">
-        <v>pending</v>
+        <v>approved</v>
       </c>
       <c r="I35" t="str">
         <v>YES 34 / NO 34</v>
       </c>
       <c r="J35" t="str">
         <v>openai/gpt-oss-20b</v>
+      </c>
+      <c r="K35" t="str">
+        <v>28360</v>
+      </c>
+      <c r="L35" t="str">
+        <v>https://6-22-shop-grasshoppergardens-press-cache.mystagingwebsite.com/?p=28360</v>
       </c>
     </row>
     <row r="36">
@@ -1345,7 +1371,7 @@
         <v>awaiting_review</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-29T14:03:01.369Z</v>
+        <v>2026-07-31T01:52:18.108Z</v>
       </c>
       <c r="G36" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0035-native-vs-cross-platform-app-development-which-should-you-ch.md</v>
@@ -1368,10 +1394,10 @@
         <v>How to Scope an MVP App Without Losing the Core Idea</v>
       </c>
       <c r="C37" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D37" t="str">
-        <v>awaiting_review</v>
+        <v>error</v>
       </c>
       <c r="E37" t="str">
         <v>2026-07-29T14:04:50.474Z</v>
@@ -1397,16 +1423,16 @@
         <v>Mobile Payment Integration: What Businesses Need to Plan For</v>
       </c>
       <c r="C38" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D38" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-29T14:06:37.717Z</v>
+        <v>2026-07-31T02:00:25.997Z</v>
       </c>
       <c r="G38" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0037-mobile-payment-integration-what-businesses-need-to-plan-for.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0037-mobile-payment-integration-planning.md</v>
       </c>
       <c r="H38" t="str">
         <v>pending</v>
@@ -1426,13 +1452,13 @@
         <v>Push Notification Best Practices: How to Increase App Engagement</v>
       </c>
       <c r="C39" t="str">
-        <v>short</v>
+        <v>long</v>
       </c>
       <c r="D39" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-29T14:08:15.500Z</v>
+        <v>2026-07-31T02:04:57.812Z</v>
       </c>
       <c r="G39" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0038-push-notification-best-practices-increase-app-engagement.md</v>
@@ -1455,13 +1481,13 @@
         <v>Mobile App Analytics: Key Metrics to Track After Launch</v>
       </c>
       <c r="C40" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D40" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-29T14:10:01.638Z</v>
+        <v>2026-07-31T02:08:56.900Z</v>
       </c>
       <c r="G40" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0039-mobile-app-analytics-key-metrics-after-launch.md</v>
@@ -1484,16 +1510,16 @@
         <v>App Maintenance Checklist: What Happens After Your App Launches</v>
       </c>
       <c r="C41" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D41" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-29T14:11:46.559Z</v>
+        <v>2026-07-31T02:12:33.805Z</v>
       </c>
       <c r="G41" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0040-app-maintenance-checklist-after-launch.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0040-app-maintenance-checklist-what-happens-after-your-app-launch.md</v>
       </c>
       <c r="H41" t="str">
         <v>pending</v>
@@ -1519,10 +1545,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-29T14:13:53.886Z</v>
+        <v>2026-07-31T02:15:27.591Z</v>
       </c>
       <c r="G42" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0041-technical-seo-audit-checklist-first-review.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0041-technical-seo-audit-checklist-review-first.md</v>
       </c>
       <c r="H42" t="str">
         <v>pending</v>
@@ -1542,16 +1568,16 @@
         <v>What Is Schema Markup and How Does It Help Your Website?</v>
       </c>
       <c r="C43" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D43" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-29T14:15:41.404Z</v>
+        <v>2026-07-31T02:18:29.098Z</v>
       </c>
       <c r="G43" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0042-schema-markup-website-benefits.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0042-what-is-schema-markup-and-how-does-it-help-your-website.md</v>
       </c>
       <c r="H43" t="str">
         <v>pending</v>
@@ -1571,13 +1597,13 @@
         <v>How to Improve Website Indexing: A Practical Google Search Console Guide</v>
       </c>
       <c r="C44" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D44" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-29T14:17:26.602Z</v>
+        <v>2026-07-31T02:21:24.813Z</v>
       </c>
       <c r="G44" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0043-improve-website-indexing-google-search-console-guide.md</v>
@@ -1600,16 +1626,16 @@
         <v>Crawl Budget Explained: When It Matters and How to Improve Crawlability</v>
       </c>
       <c r="C45" t="str">
-        <v>short</v>
+        <v>long</v>
       </c>
       <c r="D45" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-29T14:19:01.458Z</v>
+        <v>2026-07-31T02:24:57.419Z</v>
       </c>
       <c r="G45" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0044-crawl-budget-explained-improve-crawlability.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0044-crawl-budget-explained-when-it-matters-how-to-improve-crawla.md</v>
       </c>
       <c r="H45" t="str">
         <v>pending</v>
@@ -1635,10 +1661,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-29T14:21:12.494Z</v>
+        <v>2026-07-31T02:29:01.279Z</v>
       </c>
       <c r="G46" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0045-local-seo-checklist-service-businesses.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0045-local-seo-checklist-for-service-businesses.md</v>
       </c>
       <c r="H46" t="str">
         <v>pending</v>
@@ -1664,10 +1690,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-29T14:23:30.850Z</v>
+        <v>2026-07-31T02:32:21.834Z</v>
       </c>
       <c r="G47" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0046-seo-website-migration-checklist-protect-rankings.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0046-seo-website-migration-checklist-protect-rankings-during-rede.md</v>
       </c>
       <c r="H47" t="str">
         <v>pending</v>
@@ -1687,16 +1713,16 @@
         <v>Internal Linking Strategy for SEO: How to Connect Service Pages and Blog Content</v>
       </c>
       <c r="C48" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D48" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-29T14:25:25.443Z</v>
+        <v>2026-07-31T02:35:25.149Z</v>
       </c>
       <c r="G48" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0047-internal-linking-strategy-service-pages-blog-content.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0047-internal-linking-strategy-seo-connect-service-pages-blog-con.md</v>
       </c>
       <c r="H48" t="str">
         <v>pending</v>
@@ -1716,16 +1742,16 @@
         <v>Core Web Vitals for SEO: What They Mean for Business Websites</v>
       </c>
       <c r="C49" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D49" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-29T14:27:12.563Z</v>
+        <v>2026-07-31T02:39:27.829Z</v>
       </c>
       <c r="G49" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0048-core-web-vitals-seo-business-websites.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0048-core-web-vitals-for-seo-what-they-mean-for-business-websites.md</v>
       </c>
       <c r="H49" t="str">
         <v>pending</v>
@@ -1745,13 +1771,13 @@
         <v>GA4 Setup Checklist for a New Website</v>
       </c>
       <c r="C50" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D50" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-29T14:28:58.972Z</v>
+        <v>2026-07-31T02:42:53.266Z</v>
       </c>
       <c r="G50" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0049-ga4-setup-checklist-new-website.md</v>
@@ -1774,22 +1800,22 @@
         <v>Google Tag Manager Setup Guide: A Clean Foundation for Reliable Tracking</v>
       </c>
       <c r="C51" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D51" t="str">
-        <v>posted</v>
+        <v>awaiting_review</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-29T14:30:46.463Z</v>
+        <v>2026-07-31T02:45:55.318Z</v>
       </c>
       <c r="F51" t="str">
         <v>2026-07-29T15:17:11.689Z</v>
       </c>
       <c r="G51" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0050-google-tag-manager-setup-guide-clean-foundation.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0050-google-tag-manager-setup-guide-clean-foundation-reliable-tra.md</v>
       </c>
       <c r="H51" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I51" t="str">
         <v>YES 50 / NO 50</v>
@@ -1812,22 +1838,22 @@
         <v>How to Audit GA4: Find Tracking Errors Before They Affect Decisions</v>
       </c>
       <c r="C52" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D52" t="str">
-        <v>posted</v>
+        <v>awaiting_review</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-29T14:32:34.345Z</v>
+        <v>2026-07-31T02:50:51.779Z</v>
       </c>
       <c r="F52" t="str">
         <v>2026-07-29T15:15:55.928Z</v>
       </c>
       <c r="G52" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0051-audit-ga4-find-tracking-errors.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0051-audit-ga4-find-tracking-errors-before-they-affect-decisions.md</v>
       </c>
       <c r="H52" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I52" t="str">
         <v>YES 51 / NO 51</v>
@@ -1850,13 +1876,13 @@
         <v>How to Choose a Web Design Company: 12 Questions to Ask Before You Hire</v>
       </c>
       <c r="C53" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D53" t="str">
-        <v>posted</v>
+        <v>awaiting_review</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-29T16:03:59.550Z</v>
+        <v>2026-07-31T02:54:45.355Z</v>
       </c>
       <c r="F53" t="str">
         <v>2026-07-29T16:07:00.244Z</v>
@@ -1865,7 +1891,7 @@
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0052-choose-web-design-company-12-questions.md</v>
       </c>
       <c r="H53" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I53" t="str">
         <v>YES 52 / NO 52</v>
@@ -1894,7 +1920,7 @@
         <v>awaiting_review</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-29T16:08:17.513Z</v>
+        <v>2026-07-31T02:58:52.655Z</v>
       </c>
       <c r="G54" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0053-responsive-web-design-best-practices-mobile-first-business-w.md</v>
@@ -1923,10 +1949,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-29T16:15:01.606Z</v>
+        <v>2026-07-31T03:03:18.018Z</v>
       </c>
       <c r="G55" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0054-wordpress-vs-webflow-best-cms-growing-business.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0054-wordpress-vs-webflow-cms-for-growing-business.md</v>
       </c>
       <c r="H55" t="str">
         <v>pending</v>
@@ -1949,10 +1975,10 @@
         <v>long</v>
       </c>
       <c r="D56" t="str">
-        <v>posted</v>
+        <v>awaiting_review</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-29T18:34:54.584Z</v>
+        <v>2026-07-31T03:06:52.193Z</v>
       </c>
       <c r="F56" t="str">
         <v>2026-07-29T18:52:44.195Z</v>
@@ -1961,7 +1987,7 @@
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0055-wordpress-vs-squarespace-which-platform-fits-your-business.md</v>
       </c>
       <c r="H56" t="str">
-        <v>approved</v>
+        <v>pending</v>
       </c>
       <c r="I56" t="str">
         <v>YES 55 / NO 55</v>
@@ -1990,7 +2016,7 @@
         <v>awaiting_review</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-29T18:54:00.132Z</v>
+        <v>2026-07-31T03:10:59.938Z</v>
       </c>
       <c r="G57" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0056-headless-wordpress-explained-benefits-costs-when-it-makes-se.md</v>
@@ -2013,13 +2039,13 @@
         <v>Website Redesign ROI: How to Build a Business Case for a Better Website</v>
       </c>
       <c r="C58" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D58" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-29T19:05:36.781Z</v>
+        <v>2026-07-31T03:15:00.746Z</v>
       </c>
       <c r="G58" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0057-website-redesign-roi-business-case.md</v>
@@ -2042,13 +2068,13 @@
         <v>What Is a Website Discovery Phase? A Guide to Strategy Before Design</v>
       </c>
       <c r="C59" t="str">
-        <v>medium</v>
+        <v>long</v>
       </c>
       <c r="D59" t="str">
         <v>awaiting_review</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-29T19:07:32.852Z</v>
+        <v>2026-07-31T03:18:00.130Z</v>
       </c>
       <c r="G59" t="str">
         <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0058-website-discovery-phase-guide.md</v>
@@ -2077,10 +2103,10 @@
         <v>awaiting_review</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-29T20:24:37.237Z</v>
+        <v>2026-07-31T03:21:35.311Z</v>
       </c>
       <c r="G60" t="str">
-        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0059-ux-audit-checklist-find-friction-cost-leads.md</v>
+        <v>/Users/dev/Developer/repos/WP-blog-agent/data/drafts/blog-0059-ux-audit-checklist-find-friction-costs-leads.md</v>
       </c>
       <c r="H60" t="str">
         <v>pending</v>
@@ -2100,10 +2126,10 @@
         <v>Mobile-First Web Design: What It Means and Why Businesses Need It</v>
       </c>
       <c r="C61" t="str">
-        <v>short</v>
+        <v>long</v>
       </c>
       <c r="D61" t="str">
-        <v>awaiting_review</v>
+        <v>generating</v>
       </c>
       <c r="E61" t="str">
         <v>2026-07-29T21:09:00.049Z</v>
